--- a/output_files/核心能力與教育目標分析/碩士班_核心能力與教育目標達成度分析_20260423.xlsx
+++ b/output_files/核心能力與教育目標分析/碩士班_核心能力與教育目標達成度分析_20260423.xlsx
@@ -1130,7 +1130,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>書報討論[93.5], 書報討論[94.2], 光電半導體元件專題[95.0], 固態電子元件（一）[79.1], 微機電系統[88.6], 電子陶瓷[87.2], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 積體電路技術[85.6], 二維材料合成專題[87.0], 高速電子與光電元件[95.0], 切換系統控制專題[88.0], 非線性系統[81.6], 線性系統分析[81.7], 線性系統專題[91.0], 智慧型機器人專題（一）[95.0], 類比濾波器理論與設計[87.5], 工程軟體應用與設計[78.9], 智慧型控制[81.8], 高等模糊控制[90.2], 車載行動網路專題[95.0], 高等計算機結構[81.2], 無線與行動多媒體網路[86.3], 機器學習[83.8], 賽局理論與應用[77.6], 視覺辨識專題[92.3], 組合數學[84.9], 固態能量轉換[85.8], 配電管理系統專題[90.1], 高等電機機械理論分析[87.0], 電力系統運轉[82.5], 電力電子轉換器[80.0], 電力潮流分析[89.2], 電子安定器設計專題[87.8], 配電系統分析專題[95.0], 智慧電網專題[95.0], 配電自動化簡介[80.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 天線工程專題[81.8], 平面天線設計[70.6], 非線性微波電路專題[95.0], 微波積體電路專題[95.0], 電磁相容專題[91.0], 微波電路與系統[80.9], 雷達系統專題[95.0], 國際電磁波實作操練[94.5], 視訊傳輸專題[95.0], 圖形識別專題[95.0], FPGA系統設計實務[85.5], 生醫訊號處理專題[95.0], 低功率系統設計[72.8], 系統晶片設計[78.9], 積體電路佈局專題[86.3], 生醫影像研究方法[71.5], 磁共振影像：原理與應用[75.7], 臨床磁共振影像專題[91.0], 積體電路系統測試專題[95.0], 系統晶片測試[88.8], 數位通訊電路設計[87.4], 醫學影像分析專題[87.0], 腦機介面與大腦網路[82.5]</t>
+          <t>書報討論[93.5,94.2], 光電半導體元件專題[95.0], 固態電子元件（一）[79.1], 微機電系統[88.6], 電子陶瓷[87.2], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 積體電路技術[85.6], 二維材料合成專題[87.0], 高速電子與光電元件[95.0], 切換系統控制專題[88.0], 非線性系統[81.6], 線性系統分析[81.7], 線性系統專題[91.0], 智慧型機器人專題（一）[95.0], 類比濾波器理論與設計[87.5], 工程軟體應用與設計[78.9], 智慧型控制[81.8], 高等模糊控制[90.2], 車載行動網路專題[95.0], 高等計算機結構[81.2], 無線與行動多媒體網路[86.3], 機器學習[83.8], 賽局理論與應用[77.6], 視覺辨識專題[92.3], 組合數學[84.9], 固態能量轉換[85.8], 配電管理系統專題[90.1], 高等電機機械理論分析[87.0], 電力系統運轉[82.5], 電力電子轉換器[80.0], 電力潮流分析[89.2], 電子安定器設計專題[87.8], 配電系統分析專題[95.0], 智慧電網專題[95.0], 配電自動化簡介[80.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 天線工程專題[81.8], 平面天線設計[70.6], 非線性微波電路專題[95.0], 微波積體電路專題[95.0], 電磁相容專題[91.0], 微波電路與系統[80.9], 雷達系統專題[95.0], 國際電磁波實作操練[94.5], 視訊傳輸專題[95.0], 圖形識別專題[95.0], FPGA系統設計實務[85.5], 生醫訊號處理專題[95.0], 低功率系統設計[72.8], 系統晶片設計[78.9], 積體電路佈局專題[86.3], 生醫影像研究方法[71.5], 磁共振影像：原理與應用[75.7], 臨床磁共振影像專題[91.0], 積體電路系統測試專題[95.0], 系統晶片測試[88.8], 數位通訊電路設計[87.4], 醫學影像分析專題[87.0], 腦機介面與大腦網路[82.5]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1160,7 +1160,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>書報討論[93.5], 書報討論[94.2], 微機電系統[88.6], 電子陶瓷[87.2], 薄膜工程專題[95.0], 切換系統控制專題[88.0], 非線性系統[81.6], 線性系統分析[81.7], 工程軟體應用與設計[78.9], 智慧型控制[81.8], 高等模糊控制[90.2], 車載行動網路專題[95.0], 高等計算機結構[81.2], 機器學習[83.8], 賽局理論與應用[77.6], 視覺辨識專題[92.3], 組合數學[84.9], 高等電機機械理論分析[87.0], 電力系統運轉[82.5], 電力電子轉換器[80.0], 電力潮流分析[89.2], 電子安定器設計專題[87.8], 配電自動化簡介[80.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 平面天線設計[70.6], 電磁相容專題[91.0], 雷達系統專題[95.0], 視訊傳輸專題[95.0], 圖形識別專題[95.0], FPGA系統設計實務[85.5], 生醫訊號處理專題[95.0], 積體電路佈局專題[86.3], 生醫影像研究方法[71.5], 積體電路系統測試專題[95.0], 系統晶片測試[88.8], 數位通訊電路設計[87.4], 醫學影像分析專題[87.0]</t>
+          <t>書報討論[93.5,94.2], 微機電系統[88.6], 電子陶瓷[87.2], 薄膜工程專題[95.0], 切換系統控制專題[88.0], 非線性系統[81.6], 線性系統分析[81.7], 工程軟體應用與設計[78.9], 智慧型控制[81.8], 高等模糊控制[90.2], 車載行動網路專題[95.0], 高等計算機結構[81.2], 機器學習[83.8], 賽局理論與應用[77.6], 視覺辨識專題[92.3], 組合數學[84.9], 高等電機機械理論分析[87.0], 電力系統運轉[82.5], 電力電子轉換器[80.0], 電力潮流分析[89.2], 電子安定器設計專題[87.8], 配電自動化簡介[80.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 平面天線設計[70.6], 電磁相容專題[91.0], 雷達系統專題[95.0], 視訊傳輸專題[95.0], 圖形識別專題[95.0], FPGA系統設計實務[85.5], 生醫訊號處理專題[95.0], 積體電路佈局專題[86.3], 生醫影像研究方法[71.5], 積體電路系統測試專題[95.0], 系統晶片測試[88.8], 數位通訊電路設計[87.4], 醫學影像分析專題[87.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>書報討論[93.5], 書報討論[94.2], 光電半導體元件專題[95.0], 固態電子元件（一）[79.1], 微機電系統[88.6], 電子陶瓷[87.2], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 積體電路技術[85.6], 二維材料合成專題[87.0], 高速電子與光電元件[95.0], 類比濾波器理論與設計[87.5], 工程軟體應用與設計[78.9], 智慧型控制[81.8], 高等模糊控制[90.2], 車載行動網路專題[95.0], 無線與行動多媒體網路[86.3], 視覺辨識專題[92.3], 固態能量轉換[85.8], 電力電子轉換器[80.0], 電力潮流分析[89.2], 電子安定器設計專題[87.8], 配電系統分析專題[95.0], 智慧電網專題[95.0], 配電自動化簡介[80.6], 天線工程專題[81.8], 電磁相容專題[91.0], 雷達系統專題[95.0], 國際電磁波實作操練[94.5], 視訊傳輸專題[95.0], 圖形識別專題[95.0], 生醫訊號處理專題[95.0], 低功率系統設計[72.8], 系統晶片設計[78.9], 積體電路佈局專題[86.3], 臨床磁共振影像專題[91.0], 積體電路系統測試專題[95.0], 系統晶片測試[88.8], 數位通訊電路設計[87.4], 腦機介面與大腦網路[82.5]</t>
+          <t>書報討論[93.5,94.2], 光電半導體元件專題[95.0], 固態電子元件（一）[79.1], 微機電系統[88.6], 電子陶瓷[87.2], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 積體電路技術[85.6], 二維材料合成專題[87.0], 高速電子與光電元件[95.0], 類比濾波器理論與設計[87.5], 工程軟體應用與設計[78.9], 智慧型控制[81.8], 高等模糊控制[90.2], 車載行動網路專題[95.0], 無線與行動多媒體網路[86.3], 視覺辨識專題[92.3], 固態能量轉換[85.8], 電力電子轉換器[80.0], 電力潮流分析[89.2], 電子安定器設計專題[87.8], 配電系統分析專題[95.0], 智慧電網專題[95.0], 配電自動化簡介[80.6], 天線工程專題[81.8], 電磁相容專題[91.0], 雷達系統專題[95.0], 國際電磁波實作操練[94.5], 視訊傳輸專題[95.0], 圖形識別專題[95.0], 生醫訊號處理專題[95.0], 低功率系統設計[72.8], 系統晶片設計[78.9], 積體電路佈局專題[86.3], 臨床磁共振影像專題[91.0], 積體電路系統測試專題[95.0], 系統晶片測試[88.8], 數位通訊電路設計[87.4], 腦機介面與大腦網路[82.5]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[86.5], 高可靠度系統之設計、測試與應用[87.8], 書報討論[93.0], 書報討論[94.2], SOI/MOSFET設計專題[91.0], 光電元件[81.3], 固態電子元件（二）[72.8], 高等矽覆絕緣技術[93.0], 感測元件[87.2], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 寬能隙半導體與功率元件[69.5], 多變數系統控制[88.5], 非線性控制設計專題[93.4], 強韌控制專題[95.0], 最佳控制[83.5], 線性系統分析[79.0], 行動機器人[76.5], 圖型識別[76.1], 計算機網路[85.1], 無線網路資源管理專題[87.0], 電腦模擬技術與分析[95.0], 演算法設計及分析[82.0], 車載通訊網路技術與應用[95.0], 人臉辨識專題[93.4], 主動式電力濾波器[72.2], 共振式轉換器專題[95.0], 電力系統專題[93.0], 電力系統運轉[78.2], 電力品質[87.0], 電子安定器設計專題[95.0], 配電系統分析專題[89.0], 電力系統規劃[95.0], 諧振式電力電子轉換器[82.0], 高等電機暨驅控系統設計專題[95.0], 無線通訊天線設計[78.8], 無線傳輸專題[92.3], 微帶天線專題[80.7], 電磁理論[84.5], 電磁相容[84.1], 微波感測專題[95.0], 微波主動電路專題[87.0], 視訊標準專題[95.0], 低功率積體電路專題[87.0], 超大型積體電路數位訊號處理[80.0], 高等數位電路設計專題[87.0], 電腦視覺[91.2], 混合訊號積體電路設計專題[95.0], 電源管理積體電路設計[64.8], 生理訊號研究專題[84.5], 三維視覺[92.4], 醫療影像之深度學習應用專題[92.3]</t>
+          <t>生醫儀器導論[86.5], 高可靠度系統之設計、測試與應用[87.8], 書報討論[93.0,94.2], SOI/MOSFET設計專題[91.0], 光電元件[81.3], 固態電子元件（二）[72.8], 高等矽覆絕緣技術[93.0], 感測元件[87.2], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 寬能隙半導體與功率元件[69.5], 多變數系統控制[88.5], 非線性控制設計專題[93.4], 強韌控制專題[95.0], 最佳控制[83.5], 線性系統分析[79.0], 行動機器人[76.5], 圖型識別[76.1], 計算機網路[85.1], 無線網路資源管理專題[87.0], 電腦模擬技術與分析[95.0], 演算法設計及分析[82.0], 車載通訊網路技術與應用[95.0], 人臉辨識專題[93.4], 主動式電力濾波器[72.2], 共振式轉換器專題[95.0], 電力系統專題[93.0], 電力系統運轉[78.2], 電力品質[87.0], 電子安定器設計專題[95.0], 配電系統分析專題[89.0], 電力系統規劃[95.0], 諧振式電力電子轉換器[82.0], 高等電機暨驅控系統設計專題[95.0], 無線通訊天線設計[78.8], 無線傳輸專題[92.3], 微帶天線專題[80.7], 電磁理論[84.5], 電磁相容[84.1], 微波感測專題[95.0], 微波主動電路專題[87.0], 視訊標準專題[95.0], 低功率積體電路專題[87.0], 超大型積體電路數位訊號處理[80.0], 高等數位電路設計專題[87.0], 電腦視覺[91.2], 混合訊號積體電路設計專題[95.0], 電源管理積體電路設計[64.8], 生理訊號研究專題[84.5], 三維視覺[92.4], 醫療影像之深度學習應用專題[92.3]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1373,7 +1373,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[86.5], 高可靠度系統之設計、測試與應用[87.8], 書報討論[93.0], 書報討論[94.2], SOI/MOSFET設計專題[91.0], 高等矽覆絕緣技術[93.0], 感測元件[87.2], 電子元件專題（二）[95.0], 寬能隙半導體與功率元件[69.5], 非線性控制設計專題[93.4], 最佳控制[83.5], 行動機器人[76.5], 無線網路資源管理專題[87.0], 演算法設計及分析[82.0], 人臉辨識專題[93.4], 電力品質[87.0], 電子安定器設計專題[95.0], 配電系統分析專題[89.0], 電力系統規劃[95.0], 諧振式電力電子轉換器[82.0], 無線傳輸專題[92.3], 微波感測專題[95.0], 微波主動電路專題[87.0], 視訊標準專題[95.0], 低功率積體電路專題[87.0], 超大型積體電路數位訊號處理[80.0], 高等數位電路設計專題[87.0], 電腦視覺[91.2], 混合訊號積體電路設計專題[95.0], 電源管理積體電路設計[64.8], 生理訊號研究專題[84.5], 三維視覺[92.4], 醫療影像之深度學習應用專題[92.3]</t>
+          <t>生醫儀器導論[86.5], 高可靠度系統之設計、測試與應用[87.8], 書報討論[93.0,94.2], SOI/MOSFET設計專題[91.0], 高等矽覆絕緣技術[93.0], 感測元件[87.2], 電子元件專題（二）[95.0], 寬能隙半導體與功率元件[69.5], 非線性控制設計專題[93.4], 最佳控制[83.5], 行動機器人[76.5], 無線網路資源管理專題[87.0], 演算法設計及分析[82.0], 人臉辨識專題[93.4], 電力品質[87.0], 電子安定器設計專題[95.0], 配電系統分析專題[89.0], 電力系統規劃[95.0], 諧振式電力電子轉換器[82.0], 無線傳輸專題[92.3], 微波感測專題[95.0], 微波主動電路專題[87.0], 視訊標準專題[95.0], 低功率積體電路專題[87.0], 超大型積體電路數位訊號處理[80.0], 高等數位電路設計專題[87.0], 電腦視覺[91.2], 混合訊號積體電路設計專題[95.0], 電源管理積體電路設計[64.8], 生理訊號研究專題[84.5], 三維視覺[92.4], 醫療影像之深度學習應用專題[92.3]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1388,7 +1388,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[86.5], 高可靠度系統之設計、測試與應用[87.8], 書報討論[93.0], 書報討論[94.2], SOI/MOSFET設計專題[91.0], 光電元件[81.3], 固態電子元件（二）[72.8], 高等矽覆絕緣技術[93.0], 感測元件[87.2], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 寬能隙半導體與功率元件[69.5], 最佳控制[83.5], 行動機器人[76.5], 圖型識別[76.1], 無線網路資源管理專題[87.0], 電腦模擬技術與分析[95.0], 主動式電力濾波器[72.2], 電力系統專題[93.0], 電力系統運轉[78.2], 配電系統分析專題[89.0], 電力系統規劃[95.0], 諧振式電力電子轉換器[82.0], 高等電機暨驅控系統設計專題[95.0], 無線通訊天線設計[78.8], 無線傳輸專題[92.3], 微帶天線專題[80.7], 電磁相容[84.1], 微波感測專題[95.0], 視訊標準專題[95.0], 高等數位電路設計專題[87.0], 混合訊號積體電路設計專題[95.0], 電源管理積體電路設計[64.8], 生理訊號研究專題[84.5], 醫療影像之深度學習應用專題[92.3]</t>
+          <t>生醫儀器導論[86.5], 高可靠度系統之設計、測試與應用[87.8], 書報討論[93.0,94.2], SOI/MOSFET設計專題[91.0], 光電元件[81.3], 固態電子元件（二）[72.8], 高等矽覆絕緣技術[93.0], 感測元件[87.2], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 寬能隙半導體與功率元件[69.5], 最佳控制[83.5], 行動機器人[76.5], 圖型識別[76.1], 無線網路資源管理專題[87.0], 電腦模擬技術與分析[95.0], 主動式電力濾波器[72.2], 電力系統專題[93.0], 電力系統運轉[78.2], 配電系統分析專題[89.0], 電力系統規劃[95.0], 諧振式電力電子轉換器[82.0], 高等電機暨驅控系統設計專題[95.0], 無線通訊天線設計[78.8], 無線傳輸專題[92.3], 微帶天線專題[80.7], 電磁相容[84.1], 微波感測專題[95.0], 視訊標準專題[95.0], 高等數位電路設計專題[87.0], 混合訊號積體電路設計專題[95.0], 電源管理積體電路設計[64.8], 生理訊號研究專題[84.5], 醫療影像之深度學習應用專題[92.3]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -1556,7 +1556,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>書報討論[95.0], 書報討論[93.0], 光電半導體元件專題[93.4], 固態電子元件（一）[81.7], 微機電系統[84.5], 電子陶瓷[87.1], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 二維材料合成專題[87.0], 半導體薄膜技術[94.3], 高速電子與光電元件[93.5], 希爾伯特空間方法與應用[76.0], 非線性系統[81.7], 強韌控制專題[78.5], 智慧型機器人專題（一）[95.0], 智慧型控制[70.6], 智慧型控制研究專題[87.0], 圖型識別[77.1], 車載行動網路專題[95.0], 計算機網路[81.4], 賽局理論與應用[75.2], 視覺辨識專題[95.0], 組合數學[79.3], 配電管理系統專題[78.4], 電力系統運轉[71.7], 電力電子轉換器[79.1], 電力潮流分析[89.5], 電子安定器設計專題[88.6], 智慧電網專題[89.2], 電力系統規劃[83.5], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高效率高功率密度電力調節系統[87.0], 電網形成換流器專題[89.8], 天線工程專題[82.2], 平面天線設計[66.1], 非線性微波電路專題[85.3], 微波積體電路專題[95.0], 電磁相容專題[87.0], 微波電路與系統[79.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[83.4], FPGA系統設計實務[87.4], 生醫訊號處理專題[90.2], 低功率系統設計[94.2], 系統晶片設計[66.0], 通訊介面ＩＣ設計[88.2], 積體電路佈局專題[82.0], 生醫影像研究方法[85.3], 磁共振影像：原理與應用[75.7], 臨床磁共振影像專題[87.8], 積體電路系統測試專題[95.0], 系統晶片測試[87.8], 數位通訊電路設計[73.2], 醫學影像分析專題[81.3], 腦機介面與大腦網路[84.3]</t>
+          <t>書報討論[95.0,93.0], 光電半導體元件專題[93.4], 固態電子元件（一）[81.7], 微機電系統[84.5], 電子陶瓷[87.1], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 二維材料合成專題[87.0], 半導體薄膜技術[94.3], 高速電子與光電元件[93.5], 希爾伯特空間方法與應用[76.0], 非線性系統[81.7], 強韌控制專題[78.5], 智慧型機器人專題（一）[95.0], 智慧型控制[70.6], 智慧型控制研究專題[87.0], 圖型識別[77.1], 車載行動網路專題[95.0], 計算機網路[81.4], 賽局理論與應用[75.2], 視覺辨識專題[95.0], 組合數學[79.3], 配電管理系統專題[78.4], 電力系統運轉[71.7], 電力電子轉換器[79.1], 電力潮流分析[89.5], 電子安定器設計專題[88.6], 智慧電網專題[89.2], 電力系統規劃[83.5], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高效率高功率密度電力調節系統[87.0], 電網形成換流器專題[89.8], 天線工程專題[82.2], 平面天線設計[66.1], 非線性微波電路專題[85.3], 微波積體電路專題[95.0], 電磁相容專題[87.0], 微波電路與系統[79.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[83.4], FPGA系統設計實務[87.4], 生醫訊號處理專題[90.2], 低功率系統設計[94.2], 系統晶片設計[66.0], 通訊介面ＩＣ設計[88.2], 積體電路佈局專題[82.0], 生醫影像研究方法[85.3], 磁共振影像：原理與應用[75.7], 臨床磁共振影像專題[87.8], 積體電路系統測試專題[95.0], 系統晶片測試[87.8], 數位通訊電路設計[73.2], 醫學影像分析專題[81.3], 腦機介面與大腦網路[84.3]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>書報討論[95.0], 書報討論[93.0], 微機電系統[84.5], 電子陶瓷[87.1], 薄膜工程專題[95.0], 希爾伯特空間方法與應用[76.0], 非線性系統[81.7], 智慧型控制[70.6], 智慧型控制研究專題[87.0], 車載行動網路專題[95.0], 賽局理論與應用[75.2], 視覺辨識專題[95.0], 組合數學[79.3], 電力系統運轉[71.7], 電力電子轉換器[79.1], 電力潮流分析[89.5], 電子安定器設計專題[88.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 平面天線設計[66.1], 電磁相容專題[87.0], 雷達系統專題[95.0], 圖形識別專題[95.0], FPGA系統設計實務[87.4], 生醫訊號處理專題[90.2], 積體電路佈局專題[82.0], 生醫影像研究方法[85.3], 積體電路系統測試專題[95.0], 系統晶片測試[87.8], 數位通訊電路設計[73.2], 醫學影像分析專題[81.3]</t>
+          <t>書報討論[95.0,93.0], 微機電系統[84.5], 電子陶瓷[87.1], 薄膜工程專題[95.0], 希爾伯特空間方法與應用[76.0], 非線性系統[81.7], 智慧型控制[70.6], 智慧型控制研究專題[87.0], 車載行動網路專題[95.0], 賽局理論與應用[75.2], 視覺辨識專題[95.0], 組合數學[79.3], 電力系統運轉[71.7], 電力電子轉換器[79.1], 電力潮流分析[89.5], 電子安定器設計專題[88.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 平面天線設計[66.1], 電磁相容專題[87.0], 雷達系統專題[95.0], 圖形識別專題[95.0], FPGA系統設計實務[87.4], 生醫訊號處理專題[90.2], 積體電路佈局專題[82.0], 生醫影像研究方法[85.3], 積體電路系統測試專題[95.0], 系統晶片測試[87.8], 數位通訊電路設計[73.2], 醫學影像分析專題[81.3]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -1601,7 +1601,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>書報討論[95.0], 書報討論[93.0], 光電半導體元件專題[93.4], 固態電子元件（一）[81.7], 微機電系統[84.5], 電子陶瓷[87.1], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 二維材料合成專題[87.0], 半導體薄膜技術[94.3], 高速電子與光電元件[93.5], 希爾伯特空間方法與應用[76.0], 智慧型控制[70.6], 智慧型控制研究專題[87.0], 圖型識別[77.1], 車載行動網路專題[95.0], 視覺辨識專題[95.0], 電力電子轉換器[79.1], 電力潮流分析[89.5], 電子安定器設計專題[88.6], 智慧電網專題[89.2], 高效率高功率密度電力調節系統[87.0], 電網形成換流器專題[89.8], 天線工程專題[82.2], 電磁相容專題[87.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[83.4], 生醫訊號處理專題[90.2], 低功率系統設計[94.2], 系統晶片設計[66.0], 通訊介面ＩＣ設計[88.2], 積體電路佈局專題[82.0], 磁共振影像：原理與應用[75.7], 臨床磁共振影像專題[87.8], 積體電路系統測試專題[95.0], 系統晶片測試[87.8], 數位通訊電路設計[73.2], 腦機介面與大腦網路[84.3]</t>
+          <t>書報討論[95.0,93.0], 光電半導體元件專題[93.4], 固態電子元件（一）[81.7], 微機電系統[84.5], 電子陶瓷[87.1], 薄膜工程專題[95.0], 先進元件分析專題[95.0], 二維材料合成專題[87.0], 半導體薄膜技術[94.3], 高速電子與光電元件[93.5], 希爾伯特空間方法與應用[76.0], 智慧型控制[70.6], 智慧型控制研究專題[87.0], 圖型識別[77.1], 車載行動網路專題[95.0], 視覺辨識專題[95.0], 電力電子轉換器[79.1], 電力潮流分析[89.5], 電子安定器設計專題[88.6], 智慧電網專題[89.2], 高效率高功率密度電力調節系統[87.0], 電網形成換流器專題[89.8], 天線工程專題[82.2], 電磁相容專題[87.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[83.4], 生醫訊號處理專題[90.2], 低功率系統設計[94.2], 系統晶片設計[66.0], 通訊介面ＩＣ設計[88.2], 積體電路佈局專題[82.0], 磁共振影像：原理與應用[75.7], 臨床磁共振影像專題[87.8], 積體電路系統測試專題[95.0], 系統晶片測試[87.8], 數位通訊電路設計[73.2], 腦機介面與大腦網路[84.3]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2195,7 +2195,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>書報討論[93.5], 書報討論[94.4], 光電半導體元件專題[95.0], 固態電子元件（一）[77.2], 電子陶瓷[86.4], 薄膜工程專題[92.3], 先進元件分析專題[95.0], 積體電路技術[83.0], 二維材料合成專題[91.8], 低維度電子材料[92.6], 半導體薄膜技術[95.0], 氧化物電子專題[95.0], 寬能隙半導體與功率元件[91.1], 切換系統控制專題[95.0], 交直流馬達控制[93.2], 多媒體控制專題（一）[95.0], 希爾伯特空間方法與應用[93.4], 非線性系統[92.8], 線性系統分析[74.5], 智慧型控制研究專題[82.8], 圖訊識別[76.7], 人工智慧（一）[84.8], 車載行動網路專題[95.0], 機器學習[88.3], 資料探勘[77.0], 賽局理論與應用[72.8], 視覺辨識專題[95.0], 組合數學[79.2], 固態能量轉換[82.9], 配電管理系統專題[90.4], 高等電機機械理論分析[82.2], 電力系統專題[84.8], 電力系統控制與穩定度[95.0], 電子安定器設計專題[89.2], 電動車電池能量管理系統（一）[89.8], 智慧電網專題[82.5], 電力系統規劃[84.8], 天線工程專題[83.7], 平面天線設計[73.6], 高等微波元件專題[80.7], 電磁相容專題[85.3], 數值電磁學[86.0], 微波主動電路專題[85.7], 雷達系統專題[91.0], 雷達系統導論[84.5], 國際電磁波實作操練[93.4], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[84.5], 生醫訊號處理專題[93.0], 低功率系統設計[76.7], 嵌入式多核心系統與軟體[84.4], 積體電路佈局專題[83.4], 生醫影像研究方法[85.1], 磁共振影像：原理與應用[80.6], 臨床磁共振影像專題[82.0], 積體電路系統測試專題[95.0], 系統晶片測試[84.5], 數位通訊電路設計[87.3], 高等數位電路設計專題[92.3], 醫學影像分析專題[81.7], 腦機介面與大腦網路[91.8]</t>
+          <t>書報討論[93.5,94.4], 光電半導體元件專題[95.0], 固態電子元件（一）[77.2], 電子陶瓷[86.4], 薄膜工程專題[92.3], 先進元件分析專題[95.0], 積體電路技術[83.0], 二維材料合成專題[91.8], 低維度電子材料[92.6], 半導體薄膜技術[95.0], 氧化物電子專題[95.0], 寬能隙半導體與功率元件[91.1], 切換系統控制專題[95.0], 交直流馬達控制[93.2], 多媒體控制專題（一）[95.0], 希爾伯特空間方法與應用[93.4], 非線性系統[92.8], 線性系統分析[74.5], 智慧型控制研究專題[82.8], 圖訊識別[76.7], 人工智慧（一）[84.8], 車載行動網路專題[95.0], 機器學習[88.3], 資料探勘[77.0], 賽局理論與應用[72.8], 視覺辨識專題[95.0], 組合數學[79.2], 固態能量轉換[82.9], 配電管理系統專題[90.4], 高等電機機械理論分析[82.2], 電力系統專題[84.8], 電力系統控制與穩定度[95.0], 電子安定器設計專題[89.2], 電動車電池能量管理系統（一）[89.8], 智慧電網專題[82.5], 電力系統規劃[84.8], 天線工程專題[83.7], 平面天線設計[73.6], 高等微波元件專題[80.7], 電磁相容專題[85.3], 數值電磁學[86.0], 微波主動電路專題[85.7], 雷達系統專題[91.0], 雷達系統導論[84.5], 國際電磁波實作操練[93.4], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[84.5], 生醫訊號處理專題[93.0], 低功率系統設計[76.7], 嵌入式多核心系統與軟體[84.4], 積體電路佈局專題[83.4], 生醫影像研究方法[85.1], 磁共振影像：原理與應用[80.6], 臨床磁共振影像專題[82.0], 積體電路系統測試專題[95.0], 系統晶片測試[84.5], 數位通訊電路設計[87.3], 高等數位電路設計專題[92.3], 醫學影像分析專題[81.7], 腦機介面與大腦網路[91.8]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2240,7 +2240,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>書報討論[93.5], 書報討論[94.4], 光電半導體元件專題[95.0], 固態電子元件（一）[77.2], 電子陶瓷[86.4], 薄膜工程專題[92.3], 先進元件分析專題[95.0], 積體電路技術[83.0], 二維材料合成專題[91.8], 低維度電子材料[92.6], 氧化物電子專題[95.0], 寬能隙半導體與功率元件[91.1], 切換系統控制專題[95.0], 多媒體控制專題（一）[95.0], 希爾伯特空間方法與應用[93.4], 智慧型控制研究專題[82.8], 車載行動網路專題[95.0], 機器學習[88.3], 視覺辨識專題[95.0], 組合數學[79.2], 固態能量轉換[82.9], 配電管理系統專題[90.4], 高等電機機械理論分析[82.2], 電力系統專題[84.8], 電子安定器設計專題[89.2], 智慧電網專題[82.5], 天線工程專題[83.7], 平面天線設計[73.6], 電磁相容專題[85.3], 數值電磁學[86.0], 雷達系統專題[91.0], 雷達系統導論[84.5], 國際電磁波實作操練[93.4], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[84.5], 生醫訊號處理專題[93.0], 積體電路佈局專題[83.4], 磁共振影像：原理與應用[80.6], 臨床磁共振影像專題[82.0], 積體電路系統測試專題[95.0], 系統晶片測試[84.5], 腦機介面與大腦網路[91.8]</t>
+          <t>書報討論[93.5,94.4], 光電半導體元件專題[95.0], 固態電子元件（一）[77.2], 電子陶瓷[86.4], 薄膜工程專題[92.3], 先進元件分析專題[95.0], 積體電路技術[83.0], 二維材料合成專題[91.8], 低維度電子材料[92.6], 氧化物電子專題[95.0], 寬能隙半導體與功率元件[91.1], 切換系統控制專題[95.0], 多媒體控制專題（一）[95.0], 希爾伯特空間方法與應用[93.4], 智慧型控制研究專題[82.8], 車載行動網路專題[95.0], 機器學習[88.3], 視覺辨識專題[95.0], 組合數學[79.2], 固態能量轉換[82.9], 配電管理系統專題[90.4], 高等電機機械理論分析[82.2], 電力系統專題[84.8], 電子安定器設計專題[89.2], 智慧電網專題[82.5], 天線工程專題[83.7], 平面天線設計[73.6], 電磁相容專題[85.3], 數值電磁學[86.0], 雷達系統專題[91.0], 雷達系統導論[84.5], 國際電磁波實作操練[93.4], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[84.5], 生醫訊號處理專題[93.0], 積體電路佈局專題[83.4], 磁共振影像：原理與應用[80.6], 臨床磁共振影像專題[82.0], 積體電路系統測試專題[95.0], 系統晶片測試[84.5], 腦機介面與大腦網路[91.8]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2408,7 +2408,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[91.4], 高可靠度系統之設計、測試與應用[88.1], 書報討論[94.7], 書報討論[94.6], 光電元件[89.0], 固態電子元件（二）[78.3], 感測元件[90.2], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 醫用電子[89.9], 高速電子與光電元件[88.7], 氮化物半導體元件專題[95.0], 非線性控制系統設計[87.0], 非線性控制設計專題[87.2], 基礎數值最佳化[89.7], 強韌控制專題[95.0], 最佳控制[88.0], 模糊數學[75.8], 線性系統專題[78.0], 工程軟體應用與設計[82.0], 智慧型控制[91.0], 人工智慧（二）[83.7], 計算機網路[80.6], 無線網路資源管理專題[82.0], 演算法設計及分析[81.8], 網路效能分析專題[86.7], 車載通訊網路技術與應用[95.0], 3D內容生成與體感互動[95.0], 人臉辨識專題[93.0], 主動式電力濾波器[88.0], 共振式轉換器專題[91.0], 電力系統可靠度[86.2], 電力品質[87.0], 電力潮流分析[90.2], 電機機械系統設計專題[87.0], 配電系統分析專題[89.1], 智慧電網專題[91.0], 電力系統規劃[87.0], 諧振式電力電子轉換器[79.5], 非線性微波電路專題[72.3], 無線通訊天線設計[83.7], 無線傳輸專題[87.0], 微帶天線專題[83.0], 電磁理論[80.1], 數值電磁專題[87.0], 電磁相容[84.7], 微波感測專題[87.1], 視訊標準專題[95.0], 生醫訊號處理專題[85.3], 低功率積體電路專題[87.0], 系統晶片設計[83.4], 計算理論[82.2], 高等類比積體電路設計[78.5], 照明電子設計專題[89.5], 超大型積體電路數位訊號處理[84.5], 數位通訊電路設計專題[84.2], 電腦視覺[82.8], 混合訊號積體電路設計專題[81.5], 生理訊號研究專題[84.5], 生醫訊號處理[84.3], 腦機介面專題[87.8], 三維視覺[87.2]</t>
+          <t>生醫儀器導論[91.4], 高可靠度系統之設計、測試與應用[88.1], 書報討論[94.7,94.6], 光電元件[89.0], 固態電子元件（二）[78.3], 感測元件[90.2], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 醫用電子[89.9], 高速電子與光電元件[88.7], 氮化物半導體元件專題[95.0], 非線性控制系統設計[87.0], 非線性控制設計專題[87.2], 基礎數值最佳化[89.7], 強韌控制專題[95.0], 最佳控制[88.0], 模糊數學[75.8], 線性系統專題[78.0], 工程軟體應用與設計[82.0], 智慧型控制[91.0], 人工智慧（二）[83.7], 計算機網路[80.6], 無線網路資源管理專題[82.0], 演算法設計及分析[81.8], 網路效能分析專題[86.7], 車載通訊網路技術與應用[95.0], 3D內容生成與體感互動[95.0], 人臉辨識專題[93.0], 主動式電力濾波器[88.0], 共振式轉換器專題[91.0], 電力系統可靠度[86.2], 電力品質[87.0], 電力潮流分析[90.2], 電機機械系統設計專題[87.0], 配電系統分析專題[89.1], 智慧電網專題[91.0], 電力系統規劃[87.0], 諧振式電力電子轉換器[79.5], 非線性微波電路專題[72.3], 無線通訊天線設計[83.7], 無線傳輸專題[87.0], 微帶天線專題[83.0], 電磁理論[80.1], 數值電磁專題[87.0], 電磁相容[84.7], 微波感測專題[87.1], 視訊標準專題[95.0], 生醫訊號處理專題[85.3], 低功率積體電路專題[87.0], 系統晶片設計[83.4], 計算理論[82.2], 高等類比積體電路設計[78.5], 照明電子設計專題[89.5], 超大型積體電路數位訊號處理[84.5], 數位通訊電路設計專題[84.2], 電腦視覺[82.8], 混合訊號積體電路設計專題[81.5], 生理訊號研究專題[84.5], 生醫訊號處理[84.3], 腦機介面專題[87.8], 三維視覺[87.2]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2453,7 +2453,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[91.4], 高可靠度系統之設計、測試與應用[88.1], 書報討論[94.7], 書報討論[94.6], 光電元件[89.0], 固態電子元件（二）[78.3], 感測元件[90.2], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 醫用電子[89.9], 高速電子與光電元件[88.7], 氮化物半導體元件專題[95.0], 非線性控制系統設計[87.0], 強韌控制專題[95.0], 最佳控制[88.0], 工程軟體應用與設計[82.0], 智慧型控制[91.0], 計算機網路[80.6], 無線網路資源管理專題[82.0], 3D內容生成與體感互動[95.0], 主動式電力濾波器[88.0], 共振式轉換器專題[91.0], 保護電驛[87.8], 電力潮流分析[90.2], 電機機械系統設計專題[87.0], 智慧電網專題[91.0], 電力系統規劃[87.0], 諧振式電力電子轉換器[79.5], 無線通訊天線設計[83.7], 無線傳輸專題[87.0], 微帶天線專題[83.0], 電磁理論[80.1], 電磁相容[84.7], 微波感測專題[87.1], 視訊標準專題[95.0], 生醫訊號處理專題[85.3], 低功率積體電路專題[87.0], 系統晶片設計[83.4], 高等類比積體電路設計[78.5], 照明電子設計專題[89.5], 混合訊號積體電路設計專題[81.5], 生醫訊號處理[84.3], 腦機介面專題[87.8]</t>
+          <t>生醫儀器導論[91.4], 高可靠度系統之設計、測試與應用[88.1], 書報討論[94.7,94.6], 光電元件[89.0], 固態電子元件（二）[78.3], 感測元件[90.2], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 醫用電子[89.9], 高速電子與光電元件[88.7], 氮化物半導體元件專題[95.0], 非線性控制系統設計[87.0], 強韌控制專題[95.0], 最佳控制[88.0], 工程軟體應用與設計[82.0], 智慧型控制[91.0], 計算機網路[80.6], 無線網路資源管理專題[82.0], 3D內容生成與體感互動[95.0], 主動式電力濾波器[88.0], 共振式轉換器專題[91.0], 保護電驛[87.8], 電力潮流分析[90.2], 電機機械系統設計專題[87.0], 智慧電網專題[91.0], 電力系統規劃[87.0], 諧振式電力電子轉換器[79.5], 無線通訊天線設計[83.7], 無線傳輸專題[87.0], 微帶天線專題[83.0], 電磁理論[80.1], 電磁相容[84.7], 微波感測專題[87.1], 視訊標準專題[95.0], 生醫訊號處理專題[85.3], 低功率積體電路專題[87.0], 系統晶片設計[83.4], 高等類比積體電路設計[78.5], 照明電子設計專題[89.5], 混合訊號積體電路設計專題[81.5], 生醫訊號處理[84.3], 腦機介面專題[87.8]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="B2" s="7" t="inlineStr">
         <is>
-          <t>光電半導體元件專題[95.0], 固態電子元件（一）[75.9], 電子元件專題（一）[95.0], 先進元件分析專題[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 多媒體控制專題（二）[95.0], 非線性系統[89.7], 強韌控制專題[55.0], 類比濾波器理論與設計[87.1], 智慧型控制[83.6], 模糊控制研究專題[87.0], 人工智慧（一）[87.4], 車載行動網路專題[95.0], 高等計算機結構[86.1], 無線網路資源管理專題[95.0], 軟性計算[85.7], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 先進無線網路技術[88.0], 固態能量轉換[89.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力電子轉換器[79.7], 配電系統分析專題[95.0], 配電系統分析專題[90.8], 智慧電網專題[87.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高效率高功率密度電力調節系統[85.2], 天線工程專題[84.0], 平面天線設計[79.2], 高等微波元件專題[76.8], 微波積體電路專題[95.0], 電磁相容專題[85.3], 微波主動電路專題[84.5], 微波電路與系統[85.0], 雷達系統專題[92.3], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[87.9], FPGA系統設計實務[85.9], 生醫訊號處理專題[88.0], 低功率系統設計[80.2], 系統晶片設計[79.7], 通訊介面ＩＣ設計[86.0], 積體電路佈局專題[83.8], 醫學影像系統[85.8], 生醫影像研究方法[86.5], 磁共振影像：原理與應用[64.9], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 數位通訊電路設計[79.9], 高等數位電路設計專題[95.0], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
+          <t>光電半導體元件專題[95.0], 固態電子元件（一）[75.9], 電子元件專題（一）[95.0], 先進元件分析專題[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 多媒體控制專題（二）[95.0], 非線性系統[89.7], 強韌控制專題[55.0], 類比濾波器理論與設計[87.1], 智慧型控制[83.6], 模糊控制研究專題[87.0], 人工智慧（一）[87.4], 車載行動網路專題[95.0], 高等計算機結構[86.1], 無線網路資源管理專題[95.0], 軟性計算[85.7], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 先進無線網路技術[88.0], 固態能量轉換[89.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力電子轉換器[79.7], 配電系統分析專題[95.0,90.8], 智慧電網專題[87.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高效率高功率密度電力調節系統[85.2], 天線工程專題[84.0], 平面天線設計[79.2], 高等微波元件專題[76.8], 微波積體電路專題[95.0], 電磁相容專題[85.3], 微波主動電路專題[84.5], 微波電路與系統[85.0], 雷達系統專題[92.3], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[87.9], FPGA系統設計實務[85.9], 生醫訊號處理專題[88.0], 低功率系統設計[80.2], 系統晶片設計[79.7], 通訊介面ＩＣ設計[86.0], 積體電路佈局專題[83.8], 醫學影像系統[85.8], 生醫影像研究方法[86.5], 磁共振影像：原理與應用[64.9], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 數位通訊電路設計[79.9], 高等數位電路設計專題[95.0], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
         </is>
       </c>
       <c r="C2" s="8" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>書報討論[94.3], 書報討論[94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[75.9], 電子元件專題（一）[95.0], 先進元件分析專題[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 多媒體控制專題（二）[95.0], 非線性系統[89.7], 強韌控制專題[55.0], 類比濾波器理論與設計[87.1], 智慧型控制[83.6], 模糊控制研究專題[87.0], 人工智慧（一）[87.4], 車載行動網路專題[95.0], 高等計算機結構[86.1], 無線網路資源管理專題[95.0], 軟性計算[85.7], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 先進無線網路技術[88.0], 固態能量轉換[89.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力電子轉換器[79.7], 電力潮流分析[82.0], 配電系統分析專題[95.0], 配電系統分析專題[90.8], 智慧電網專題[87.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高效率高功率密度電力調節系統[85.2], 天線工程專題[84.0], 平面天線設計[79.2], 高等微波元件專題[76.8], 電磁相容專題[85.3], 微波主動電路專題[84.5], 雷達系統專題[92.3], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[87.9], FPGA系統設計實務[85.9], 生醫訊號處理專題[88.0], 低功率系統設計[80.2], 系統晶片設計[79.7], 通訊介面ＩＣ設計[86.0], 積體電路佈局專題[83.8], 醫學影像系統[85.8], 生醫影像研究方法[86.5], 磁共振影像：原理與應用[64.9], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 數位通訊電路設計[79.9], 高等數位電路設計專題[95.0], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
+          <t>書報討論[94.3,94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[75.9], 電子元件專題（一）[95.0], 先進元件分析專題[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 多媒體控制專題（二）[95.0], 非線性系統[89.7], 強韌控制專題[55.0], 類比濾波器理論與設計[87.1], 智慧型控制[83.6], 模糊控制研究專題[87.0], 人工智慧（一）[87.4], 車載行動網路專題[95.0], 高等計算機結構[86.1], 無線網路資源管理專題[95.0], 軟性計算[85.7], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 先進無線網路技術[88.0], 固態能量轉換[89.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力電子轉換器[79.7], 電力潮流分析[82.0], 配電系統分析專題[95.0,90.8], 智慧電網專題[87.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高效率高功率密度電力調節系統[85.2], 天線工程專題[84.0], 平面天線設計[79.2], 高等微波元件專題[76.8], 電磁相容專題[85.3], 微波主動電路專題[84.5], 雷達系統專題[92.3], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[87.9], FPGA系統設計實務[85.9], 生醫訊號處理專題[88.0], 低功率系統設計[80.2], 系統晶片設計[79.7], 通訊介面ＩＣ設計[86.0], 積體電路佈局專題[83.8], 醫學影像系統[85.8], 生醫影像研究方法[86.5], 磁共振影像：原理與應用[64.9], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 數位通訊電路設計[79.9], 高等數位電路設計專題[95.0], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>書報討論[94.3], 書報討論[94.3], 電子元件專題（一）[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 多媒體控制專題（二）[95.0], 非線性系統[89.7], 強韌控制專題[55.0], 類比濾波器理論與設計[87.1], 智慧型控制[83.6], 模糊控制研究專題[87.0], 車載行動網路專題[95.0], 高等計算機結構[86.1], 無線網路資源管理專題[95.0], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力潮流分析[82.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高等微波元件專題[76.8], 電磁相容專題[85.3], 微波主動電路專題[84.5], 雷達系統專題[92.3], 視訊通訊[95.0], FPGA系統設計實務[85.9], 生醫訊號處理專題[88.0], 積體電路佈局專題[83.8], 生醫影像研究方法[86.5], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 數位通訊電路設計[79.9], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
+          <t>書報討論[94.3,94.3], 電子元件專題（一）[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 多媒體控制專題（二）[95.0], 非線性系統[89.7], 強韌控制專題[55.0], 類比濾波器理論與設計[87.1], 智慧型控制[83.6], 模糊控制研究專題[87.0], 車載行動網路專題[95.0], 高等計算機結構[86.1], 無線網路資源管理專題[95.0], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力潮流分析[82.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高等微波元件專題[76.8], 電磁相容專題[85.3], 微波主動電路專題[84.5], 雷達系統專題[92.3], 視訊通訊[95.0], FPGA系統設計實務[85.9], 生醫訊號處理專題[88.0], 積體電路佈局專題[83.8], 生醫影像研究方法[86.5], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 數位通訊電路設計[79.9], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>書報討論[94.3], 書報討論[94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[75.9], 電子元件專題（一）[95.0], 先進元件分析專題[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 智慧型控制[83.6], 模糊控制研究專題[87.0], 人工智慧（一）[87.4], 車載行動網路專題[95.0], 軟性計算[85.7], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 固態能量轉換[89.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力電子轉換器[79.7], 電力潮流分析[82.0], 配電系統分析專題[95.0], 配電系統分析專題[90.8], 智慧電網專題[87.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 高效率高功率密度電力調節系統[85.2], 天線工程專題[84.0], 平面天線設計[79.2], 微波積體電路專題[95.0], 電磁相容專題[85.3], 雷達系統專題[92.3], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[87.9], 生醫訊號處理專題[88.0], 低功率系統設計[80.2], 系統晶片設計[79.7], 通訊介面ＩＣ設計[86.0], 積體電路佈局專題[83.8], 醫學影像系統[85.8], 磁共振影像：原理與應用[64.9], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 高等數位電路設計專題[95.0], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
+          <t>書報討論[94.3,94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[75.9], 電子元件專題（一）[95.0], 先進元件分析專題[95.0], 積體電路技術[83.7], 二維材料合成專題[89.8], 低維度電子材料[84.6], 切換系統控制專題[88.0], 智慧型控制[83.6], 模糊控制研究專題[87.0], 人工智慧（一）[87.4], 車載行動網路專題[95.0], 軟性計算[85.7], 賽局理論與應用[81.4], 視覺辨識專題[95.0], 組合數學[84.4], 固態能量轉換[89.4], 配電管理系統專題[90.2], 高等電機機械理論分析[83.7], 電力電子轉換器[79.7], 電力潮流分析[82.0], 配電系統分析專題[95.0,90.8], 智慧電網專題[87.0], 配電自動化簡介[79.8], 高等電機暨驅控系統設計專題[86.6], 高效率高功率密度電力調節系統[85.2], 天線工程專題[84.0], 平面天線設計[79.2], 微波積體電路專題[95.0], 電磁相容專題[85.3], 雷達系統專題[92.3], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[87.9], 生醫訊號處理專題[88.0], 低功率系統設計[80.2], 系統晶片設計[79.7], 通訊介面ＩＣ設計[86.0], 積體電路佈局專題[83.8], 醫學影像系統[85.8], 磁共振影像：原理與應用[64.9], 臨床磁共振影像專題[82.3], 積體電路系統測試專題[95.0], 系統晶片測試[81.3], 高等數位電路設計專題[95.0], 醫學影像分析專題[81.0], 腦機介面與大腦網路[78.0]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>高可靠度系統之設計、測試與應用[81.3], 書報討論[93.2], 書報討論[94.2], 光電元件[84.9], 固態電子元件（二）[83.5], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[86.7], 醫用電子[78.3], 高速電子與光電元件[80.7], 交直流馬達控制[88.1], 希爾伯特空間方法與應用[85.6], 非線性控制設計專題[95.0], 最佳控制[93.7], 線性系統專題[84.5], 機器人學[71.5], 圖訊識別[73.7], 工程軟體設計實務[87.0], 計算機網路[83.4], 無線網路資源管理專題[84.0], 電腦模擬技術與分析[95.0], 演算法設計及分析[75.7], 網路效能分析專題[86.6], 車載通訊網路技術與應用[84.0], 3D內容生成與體感互動[95.0], 人臉辨識專題[93.0], 先進行動通訊系統[83.8], 隨機與近似演算法[84.5], 主動式電力濾波器[89.5], 共振式轉換器專題[95.0], 電力系統運轉[87.4], 電力電子電路[89.5], 電子安定器設計專題[95.0], 電機機械系統設計專題[84.5], 配電系統分析專題[87.0], 智慧電網專題[95.0], 電力系統規劃[82.0], 諧振式電力電子轉換器[70.1], 非線性微波電路專題[82.0], 無線通訊天線設計[89.0], 無線傳輸專題[87.0], 微帶天線專題[89.7], 電磁理論[68.1], 電磁相容[82.0], 微波感測專題[88.8], 雷達系統導論[82.3], 視訊標準專題[95.0], 低功率積體電路專題[85.6], 高等類比積體電路設計[82.4], 嵌入式多核心系統與軟體[83.5], 照明電子設計專題[86.7], 超大型積體電路數位訊號處理[95.0], 電腦視覺[83.2], 混合訊號積體電路設計專題[87.2], 生理訊號研究專題[83.0], 生醫訊號處理[83.1], 腦機介面專題[87.0], 三維視覺[85.8]</t>
+          <t>高可靠度系統之設計、測試與應用[81.3], 書報討論[93.2,94.2], 光電元件[84.9], 固態電子元件（二）[83.5], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[86.7], 醫用電子[78.3], 高速電子與光電元件[80.7], 交直流馬達控制[88.1], 希爾伯特空間方法與應用[85.6], 非線性控制設計專題[95.0], 最佳控制[93.7], 線性系統專題[84.5], 機器人學[71.5], 圖訊識別[73.7], 工程軟體設計實務[87.0], 計算機網路[83.4], 無線網路資源管理專題[84.0], 電腦模擬技術與分析[95.0], 演算法設計及分析[75.7], 網路效能分析專題[86.6], 車載通訊網路技術與應用[84.0], 3D內容生成與體感互動[95.0], 人臉辨識專題[93.0], 先進行動通訊系統[83.8], 隨機與近似演算法[84.5], 主動式電力濾波器[89.5], 共振式轉換器專題[95.0], 電力系統運轉[87.4], 電力電子電路[89.5], 電子安定器設計專題[95.0], 電機機械系統設計專題[84.5], 配電系統分析專題[87.0], 智慧電網專題[95.0], 電力系統規劃[82.0], 諧振式電力電子轉換器[70.1], 非線性微波電路專題[82.0], 無線通訊天線設計[89.0], 無線傳輸專題[87.0], 微帶天線專題[89.7], 電磁理論[68.1], 電磁相容[82.0], 微波感測專題[88.8], 雷達系統導論[82.3], 視訊標準專題[95.0], 低功率積體電路專題[85.6], 高等類比積體電路設計[82.4], 嵌入式多核心系統與軟體[83.5], 照明電子設計專題[86.7], 超大型積體電路數位訊號處理[95.0], 電腦視覺[83.2], 混合訊號積體電路設計專題[87.2], 生理訊號研究專題[83.0], 生醫訊號處理[83.1], 腦機介面專題[87.0], 三維視覺[85.8]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>高可靠度系統之設計、測試與應用[81.3], 書報討論[93.2], 書報討論[94.2], 固態電子元件（二）[83.5], 電子元件專題（二）[91.0], 先進元件可靠度專題[95.0], 固態電子元件（三）[95.0], 醫用電子[78.3], 交直流馬達控制[88.1], 希爾伯特空間方法與應用[85.6], 非線性控制設計專題[95.0], 最佳控制[93.7], 線性系統專題[84.5], 機器人學[71.5], 圖訊識別[73.7], 工程軟體設計實務[87.0], 無線網路資源管理專題[84.0], 電腦模擬技術與分析[95.0], 演算法設計及分析[75.7], 車載通訊網路技術與應用[84.0], 3D內容生成與體感互動[95.0], 人臉辨識專題[93.0], 隨機與近似演算法[84.5], 電力電子電路[89.5], 電子安定器設計專題[95.0], 電機機械系統設計專題[84.5], 電力系統規劃[82.0], 無線通訊天線設計[89.0], 無線傳輸專題[87.0], 微帶天線專題[89.7], 微波感測專題[88.8], 雷達系統導論[82.3], 視訊標準專題[95.0], 低功率積體電路專題[85.6], 高等類比積體電路設計[82.4], 嵌入式多核心系統與軟體[83.5], 照明電子設計專題[86.7], 電腦視覺[83.2], 混合訊號積體電路設計專題[87.2], 生理訊號研究專題[83.0], 生醫訊號處理[83.1], 腦機介面專題[87.0], 三維視覺[85.8]</t>
+          <t>高可靠度系統之設計、測試與應用[81.3], 書報討論[93.2,94.2], 固態電子元件（二）[83.5], 電子元件專題（二）[91.0], 先進元件可靠度專題[95.0], 固態電子元件（三）[95.0], 醫用電子[78.3], 交直流馬達控制[88.1], 希爾伯特空間方法與應用[85.6], 非線性控制設計專題[95.0], 最佳控制[93.7], 線性系統專題[84.5], 機器人學[71.5], 圖訊識別[73.7], 工程軟體設計實務[87.0], 無線網路資源管理專題[84.0], 電腦模擬技術與分析[95.0], 演算法設計及分析[75.7], 車載通訊網路技術與應用[84.0], 3D內容生成與體感互動[95.0], 人臉辨識專題[93.0], 隨機與近似演算法[84.5], 電力電子電路[89.5], 電子安定器設計專題[95.0], 電機機械系統設計專題[84.5], 電力系統規劃[82.0], 無線通訊天線設計[89.0], 無線傳輸專題[87.0], 微帶天線專題[89.7], 微波感測專題[88.8], 雷達系統導論[82.3], 視訊標準專題[95.0], 低功率積體電路專題[85.6], 高等類比積體電路設計[82.4], 嵌入式多核心系統與軟體[83.5], 照明電子設計專題[86.7], 電腦視覺[83.2], 混合訊號積體電路設計專題[87.2], 生理訊號研究專題[83.0], 生醫訊號處理[83.1], 腦機介面專題[87.0], 三維視覺[85.8]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -2879,7 +2879,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>高可靠度系統之設計、測試與應用[81.3], 書報討論[93.2], 書報討論[94.2], 光電元件[84.9], 固態電子元件（二）[83.5], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[86.7], 醫用電子[78.3], 高速電子與光電元件[80.7], 希爾伯特空間方法與應用[85.6], 最佳控制[93.7], 機器人學[71.5], 圖訊識別[73.7], 工程軟體設計實務[87.0], 無線網路資源管理專題[84.0], 電腦模擬技術與分析[95.0], 車載通訊網路技術與應用[84.0], 3D內容生成與體感互動[95.0], 隨機與近似演算法[84.5], 主動式電力濾波器[89.5], 共振式轉換器專題[95.0], 電力系統運轉[87.4], 電機機械系統設計專題[84.5], 配電系統分析專題[87.0], 智慧電網專題[95.0], 電力系統規劃[82.0], 諧振式電力電子轉換器[70.1], 無線通訊天線設計[89.0], 無線傳輸專題[87.0], 微帶天線專題[89.7], 電磁相容[82.0], 微波感測專題[88.8], 視訊標準專題[95.0], 低功率積體電路專題[85.6], 高等類比積體電路設計[82.4], 照明電子設計專題[86.7], 超大型積體電路數位訊號處理[95.0], 電腦視覺[83.2], 混合訊號積體電路設計專題[87.2], 生理訊號研究專題[83.0], 三維視覺[85.8]</t>
+          <t>高可靠度系統之設計、測試與應用[81.3], 書報討論[93.2,94.2], 光電元件[84.9], 固態電子元件（二）[83.5], 電子元件專題（二）[91.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[86.7], 醫用電子[78.3], 高速電子與光電元件[80.7], 希爾伯特空間方法與應用[85.6], 最佳控制[93.7], 機器人學[71.5], 圖訊識別[73.7], 工程軟體設計實務[87.0], 無線網路資源管理專題[84.0], 電腦模擬技術與分析[95.0], 車載通訊網路技術與應用[84.0], 3D內容生成與體感互動[95.0], 隨機與近似演算法[84.5], 主動式電力濾波器[89.5], 共振式轉換器專題[95.0], 電力系統運轉[87.4], 電機機械系統設計專題[84.5], 配電系統分析專題[87.0], 智慧電網專題[95.0], 電力系統規劃[82.0], 諧振式電力電子轉換器[70.1], 無線通訊天線設計[89.0], 無線傳輸專題[87.0], 微帶天線專題[89.7], 電磁相容[82.0], 微波感測專題[88.8], 視訊標準專題[95.0], 低功率積體電路專題[85.6], 高等類比積體電路設計[82.4], 照明電子設計專題[86.7], 超大型積體電路數位訊號處理[95.0], 電腦視覺[83.2], 混合訊號積體電路設計專題[87.2], 生理訊號研究專題[83.0], 三維視覺[85.8]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -3047,7 +3047,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>書報討論[94.2], 書報討論[94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[79.9], 微機電系統[89.7], 先進元件分析專題[95.0], 積體電路技術[83.5], 二維材料合成專題[87.0], 低維度電子材料[84.8], 切換系統控制專題[87.8], 非線性系統[91.8], 線性系統分析[79.3], 類比濾波器理論與設計[84.9], 工程軟體應用與設計[66.9], 智慧型控制[75.3], 高等模糊控制[76.5], 人工智慧（一）[82.6], 車載行動網路專題[80.0], 高等計算機結構[89.7], 賽局理論與應用[77.1], 視覺辨識專題[89.0], 組合數學[80.3], 固態能量轉換[83.4], 配電管理系統專題[82.0], 高等電機機械理論分析[88.0], 電力電子轉換器[77.6], 電力潮流分析[82.7], 配電系統分析專題[95.0], 智慧電網專題[90.8], 電力系統規劃[80.7], 高等電機暨驅控系統設計專題[78.0], 再生能源和電網電壓調節的電力轉換器專題[95.0], 天線工程專題[81.8], 平面天線設計[73.1], 高等微波元件專題[85.3], 微波主動電路專題[91.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], 影像處理專題[89.0], ＣＭＯＳ射頻電路設計專題[85.8], FPGA系統設計實務[77.1], 生醫訊號處理專題[87.0], 低功率系統設計[84.2], 系統晶片設計[80.4], 積體電路佈局專題[95.0], 生醫影像研究方法[74.7], 磁共振影像：原理與應用[74.9], 臨床磁共振影像專題[87.5], 積體電路系統測試專題[95.0], 系統晶片測試[80.8], 高等數位電路設計專題[82.6], 醫學影像分析專題[87.0], 腦機介面與大腦網路[89.3]</t>
+          <t>書報討論[94.2,94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[79.9], 微機電系統[89.7], 先進元件分析專題[95.0], 積體電路技術[83.5], 二維材料合成專題[87.0], 低維度電子材料[84.8], 切換系統控制專題[87.8], 非線性系統[91.8], 線性系統分析[79.3], 類比濾波器理論與設計[84.9], 工程軟體應用與設計[66.9], 智慧型控制[75.3], 高等模糊控制[76.5], 人工智慧（一）[82.6], 車載行動網路專題[80.0], 高等計算機結構[89.7], 賽局理論與應用[77.1], 視覺辨識專題[89.0], 組合數學[80.3], 固態能量轉換[83.4], 配電管理系統專題[82.0], 高等電機機械理論分析[88.0], 電力電子轉換器[77.6], 電力潮流分析[82.7], 配電系統分析專題[95.0], 智慧電網專題[90.8], 電力系統規劃[80.7], 高等電機暨驅控系統設計專題[78.0], 再生能源和電網電壓調節的電力轉換器專題[95.0], 天線工程專題[81.8], 平面天線設計[73.1], 高等微波元件專題[85.3], 微波主動電路專題[91.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], 影像處理專題[89.0], ＣＭＯＳ射頻電路設計專題[85.8], FPGA系統設計實務[77.1], 生醫訊號處理專題[87.0], 低功率系統設計[84.2], 系統晶片設計[80.4], 積體電路佈局專題[95.0], 生醫影像研究方法[74.7], 磁共振影像：原理與應用[74.9], 臨床磁共振影像專題[87.5], 積體電路系統測試專題[95.0], 系統晶片測試[80.8], 高等數位電路設計專題[82.6], 醫學影像分析專題[87.0], 腦機介面與大腦網路[89.3]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -3077,7 +3077,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>書報討論[94.2], 書報討論[94.3], 微機電系統[89.7], 積體電路技術[83.5], 二維材料合成專題[87.0], 低維度電子材料[84.8], 切換系統控制專題[87.8], 非線性系統[91.8], 線性系統分析[79.3], 類比濾波器理論與設計[84.9], 智慧型控制[75.3], 高等模糊控制[76.5], 人工智慧（一）[82.6], 車載行動網路專題[80.0], 高等計算機結構[89.7], 賽局理論與應用[77.1], 視覺辨識專題[89.0], 組合數學[80.3], 配電管理系統專題[82.0], 高等電機機械理論分析[88.0], 電力潮流分析[82.7], 高等電機暨驅控系統設計專題[78.0], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高等微波元件專題[85.3], 微波主動電路專題[91.0], 雷達系統專題[95.0], 視訊通訊[95.0], 影像處理專題[89.0], FPGA系統設計實務[77.1], 生醫訊號處理專題[87.0], 積體電路佈局專題[95.0], 生醫影像研究方法[74.7], 臨床磁共振影像專題[87.5], 積體電路系統測試專題[95.0], 系統晶片測試[80.8], 醫學影像分析專題[87.0], 生理學[71.9], 腦機介面與大腦網路[89.3]</t>
+          <t>書報討論[94.2,94.3], 微機電系統[89.7], 積體電路技術[83.5], 二維材料合成專題[87.0], 低維度電子材料[84.8], 切換系統控制專題[87.8], 非線性系統[91.8], 線性系統分析[79.3], 類比濾波器理論與設計[84.9], 智慧型控制[75.3], 高等模糊控制[76.5], 人工智慧（一）[82.6], 車載行動網路專題[80.0], 高等計算機結構[89.7], 賽局理論與應用[77.1], 視覺辨識專題[89.0], 組合數學[80.3], 配電管理系統專題[82.0], 高等電機機械理論分析[88.0], 電力潮流分析[82.7], 高等電機暨驅控系統設計專題[78.0], 再生能源和電網電壓調節的電力轉換器專題[95.0], 高等微波元件專題[85.3], 微波主動電路專題[91.0], 雷達系統專題[95.0], 視訊通訊[95.0], 影像處理專題[89.0], FPGA系統設計實務[77.1], 生醫訊號處理專題[87.0], 積體電路佈局專題[95.0], 生醫影像研究方法[74.7], 臨床磁共振影像專題[87.5], 積體電路系統測試專題[95.0], 系統晶片測試[80.8], 醫學影像分析專題[87.0], 生理學[71.9], 腦機介面與大腦網路[89.3]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -3092,7 +3092,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>書報討論[94.2], 書報討論[94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[79.9], 微機電系統[89.7], 先進元件分析專題[95.0], 積體電路技術[83.5], 二維材料合成專題[87.0], 低維度電子材料[84.8], 切換系統控制專題[87.8], 工程軟體應用與設計[66.9], 智慧型控制[75.3], 高等模糊控制[76.5], 人工智慧（一）[82.6], 車載行動網路專題[80.0], 賽局理論與應用[77.1], 視覺辨識專題[89.0], 組合數學[80.3], 固態能量轉換[83.4], 配電管理系統專題[82.0], 高等電機機械理論分析[88.0], 電力電子轉換器[77.6], 電力潮流分析[82.7], 配電系統分析專題[95.0], 智慧電網專題[90.8], 高等電機暨驅控系統設計專題[78.0], 天線工程專題[81.8], 平面天線設計[73.1], 微波積體電路專題[95.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[85.8], 生醫訊號處理專題[87.0], 低功率系統設計[84.2], 系統晶片設計[80.4], 積體電路佈局專題[95.0], 磁共振影像：原理與應用[74.9], 臨床磁共振影像專題[87.5], 積體電路系統測試專題[95.0], 系統晶片測試[80.8], 高等數位電路設計專題[82.6], 醫學影像分析專題[87.0], 腦機介面與大腦網路[89.3]</t>
+          <t>書報討論[94.2,94.3], 光電半導體元件專題[95.0], 固態電子元件（一）[79.9], 微機電系統[89.7], 先進元件分析專題[95.0], 積體電路技術[83.5], 二維材料合成專題[87.0], 低維度電子材料[84.8], 切換系統控制專題[87.8], 工程軟體應用與設計[66.9], 智慧型控制[75.3], 高等模糊控制[76.5], 人工智慧（一）[82.6], 車載行動網路專題[80.0], 賽局理論與應用[77.1], 視覺辨識專題[89.0], 組合數學[80.3], 固態能量轉換[83.4], 配電管理系統專題[82.0], 高等電機機械理論分析[88.0], 電力電子轉換器[77.6], 電力潮流分析[82.7], 配電系統分析專題[95.0], 智慧電網專題[90.8], 高等電機暨驅控系統設計專題[78.0], 天線工程專題[81.8], 平面天線設計[73.1], 微波積體電路專題[95.0], 雷達系統專題[95.0], 國際電磁波實作操練[95.0], 視訊通訊[95.0], 圖形識別專題[95.0], ＣＭＯＳ射頻電路設計專題[85.8], 生醫訊號處理專題[87.0], 低功率系統設計[84.2], 系統晶片設計[80.4], 積體電路佈局專題[95.0], 磁共振影像：原理與應用[74.9], 臨床磁共振影像專題[87.5], 積體電路系統測試專題[95.0], 系統晶片測試[80.8], 高等數位電路設計專題[82.6], 醫學影像分析專題[87.0], 腦機介面與大腦網路[89.3]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
@@ -3260,7 +3260,7 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[83.8], 高可靠度系統之設計、測試與應用[83.9], 書報討論[94.0], 書報討論[93.3], 光電元件[89.5], 固態電子元件（二）[79.7], 智慧型微感測晶片設計專題[88.0], 感測元件[89.3], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 寬能隙半導體與功率元件[69.3], 希爾伯特空間方法與應用[70.7], 非線性控制設計專題[91.0], 最佳控制[95.0], 模糊數學[95.0], 線性系統專題[75.0], 機器人學[75.8], 智慧型機器人專題（二）[95.0], 人工智慧（一）[87.0], 計算機網路[76.1], 無線網路資源管理專題[95.0], 演算法設計及分析[78.6], 網路效能分析專題[82.6], 車載通訊網路技術與應用[95.0], 軟性計算[89.9], 3D內容生成與體感互動[95.0], 數據分析學專題[95.0], 人臉辨識專題[89.0], 主動式電力濾波器[95.0], 保護電驛[80.0], 電力系統可靠度[84.7], 電力系統專題[93.4], 電力品質[93.0], 電子安定器設計專題[92.3], 電機機械系統設計專題[95.0], 配電系統分析專題[86.6], 電力系統規劃[82.0], 諧振式電力電子轉換器[78.1], 非線性微波電路專題[95.0], 無線通訊天線設計[77.2], 微帶天線專題[81.5], 電磁理論[71.1], 微波感測專題[94.0], 雷達系統導論[91.5], 視訊標準專題[95.0], 低功率積體電路專題[84.8], 計算理論[86.0], 高等類比積體電路設計[79.9], 嵌入式多核心系統與軟體[87.0], 醫學影像系統[81.7], 照明電子設計專題[86.1], 超大型積體電路數位訊號處理[89.3], 電腦視覺[86.7], 混合訊號積體電路設計專題[83.6], 軟硬體協同設計之人工智慧晶片設計[81.1], 生理訊號研究專題[87.0], 生醫訊號處理[81.7], 腦機介面專題[87.0], 三維視覺[88.2]</t>
+          <t>生醫儀器導論[83.8], 高可靠度系統之設計、測試與應用[83.9], 書報討論[94.0,93.3], 光電元件[89.5], 固態電子元件（二）[79.7], 智慧型微感測晶片設計專題[88.0], 感測元件[89.3], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 寬能隙半導體與功率元件[69.3], 希爾伯特空間方法與應用[70.7], 非線性控制設計專題[91.0], 最佳控制[95.0], 模糊數學[95.0], 線性系統專題[75.0], 機器人學[75.8], 智慧型機器人專題（二）[95.0], 人工智慧（一）[87.0], 計算機網路[76.1], 無線網路資源管理專題[95.0], 演算法設計及分析[78.6], 網路效能分析專題[82.6], 車載通訊網路技術與應用[95.0], 軟性計算[89.9], 3D內容生成與體感互動[95.0], 數據分析學專題[95.0], 人臉辨識專題[89.0], 主動式電力濾波器[95.0], 保護電驛[80.0], 電力系統可靠度[84.7], 電力系統專題[93.4], 電力品質[93.0], 電子安定器設計專題[92.3], 電機機械系統設計專題[95.0], 配電系統分析專題[86.6], 電力系統規劃[82.0], 諧振式電力電子轉換器[78.1], 非線性微波電路專題[95.0], 無線通訊天線設計[77.2], 微帶天線專題[81.5], 電磁理論[71.1], 微波感測專題[94.0], 雷達系統導論[91.5], 視訊標準專題[95.0], 低功率積體電路專題[84.8], 計算理論[86.0], 高等類比積體電路設計[79.9], 嵌入式多核心系統與軟體[87.0], 醫學影像系統[81.7], 照明電子設計專題[86.1], 超大型積體電路數位訊號處理[89.3], 電腦視覺[86.7], 混合訊號積體電路設計專題[83.6], 軟硬體協同設計之人工智慧晶片設計[81.1], 生理訊號研究專題[87.0], 生醫訊號處理[81.7], 腦機介面專題[87.0], 三維視覺[88.2]</t>
         </is>
       </c>
       <c r="C3" s="8" t="n">
@@ -3290,7 +3290,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[83.8], 高可靠度系統之設計、測試與應用[83.9], 書報討論[94.0], 書報討論[93.3], 固態電子元件（二）[79.7], 智慧型微感測晶片設計專題[88.0], 感測元件[89.3], 電子元件專題（二）[95.0], 先進元件可靠度專題[95.0], 固態電子元件（三）[95.0], 希爾伯特空間方法與應用[70.7], 非線性控制設計專題[91.0], 最佳控制[95.0], 模糊數學[95.0], 線性系統專題[75.0], 機器人學[75.8], 人工智慧（一）[87.0], 無線網路資源管理專題[95.0], 演算法設計及分析[78.6], 車載通訊網路技術與應用[95.0], 3D內容生成與體感互動[95.0], 數據分析學專題[95.0], 人臉辨識專題[89.0], 數位化時代的開放式創新[70.2], 電力品質[93.0], 電子安定器設計專題[92.3], 電機機械系統設計專題[95.0], 電力系統規劃[82.0], 無線通訊天線設計[77.2], 微帶天線專題[81.5], 微波感測專題[94.0], 雷達系統導論[91.5], 視訊標準專題[95.0], 低功率積體電路專題[84.8], 計算理論[86.0], 高等類比積體電路設計[79.9], 嵌入式多核心系統與軟體[87.0], 照明電子設計專題[86.1], 電腦視覺[86.7], 混合訊號積體電路設計專題[83.6], 軟硬體協同設計之人工智慧晶片設計[81.1], 生理訊號研究專題[87.0], 生醫訊號處理[81.7], 腦機介面專題[87.0], 三維視覺[88.2]</t>
+          <t>生醫儀器導論[83.8], 高可靠度系統之設計、測試與應用[83.9], 書報討論[94.0,93.3], 固態電子元件（二）[79.7], 智慧型微感測晶片設計專題[88.0], 感測元件[89.3], 電子元件專題（二）[95.0], 先進元件可靠度專題[95.0], 固態電子元件（三）[95.0], 希爾伯特空間方法與應用[70.7], 非線性控制設計專題[91.0], 最佳控制[95.0], 模糊數學[95.0], 線性系統專題[75.0], 機器人學[75.8], 人工智慧（一）[87.0], 無線網路資源管理專題[95.0], 演算法設計及分析[78.6], 車載通訊網路技術與應用[95.0], 3D內容生成與體感互動[95.0], 數據分析學專題[95.0], 人臉辨識專題[89.0], 數位化時代的開放式創新[70.2], 電力品質[93.0], 電子安定器設計專題[92.3], 電機機械系統設計專題[95.0], 電力系統規劃[82.0], 無線通訊天線設計[77.2], 微帶天線專題[81.5], 微波感測專題[94.0], 雷達系統導論[91.5], 視訊標準專題[95.0], 低功率積體電路專題[84.8], 計算理論[86.0], 高等類比積體電路設計[79.9], 嵌入式多核心系統與軟體[87.0], 照明電子設計專題[86.1], 電腦視覺[86.7], 混合訊號積體電路設計專題[83.6], 軟硬體協同設計之人工智慧晶片設計[81.1], 生理訊號研究專題[87.0], 生醫訊號處理[81.7], 腦機介面專題[87.0], 三維視覺[88.2]</t>
         </is>
       </c>
       <c r="C5" s="8" t="n">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>生醫儀器導論[83.8], 高可靠度系統之設計、測試與應用[83.9], 書報討論[94.0], 書報討論[93.3], 光電元件[89.5], 固態電子元件（二）[79.7], 智慧型微感測晶片設計專題[88.0], 感測元件[89.3], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 寬能隙半導體與功率元件[69.3], 希爾伯特空間方法與應用[70.7], 最佳控制[95.0], 模糊數學[95.0], 機器人學[75.8], 人工智慧（一）[87.0], 無線網路資源管理專題[95.0], 車載通訊網路技術與應用[95.0], 軟性計算[89.9], 3D內容生成與體感互動[95.0], 數據分析學專題[95.0], 數位化時代的開放式創新[70.2], 主動式電力濾波器[95.0], 電力系統專題[93.4], 電機機械系統設計專題[95.0], 配電系統分析專題[86.6], 電力系統規劃[82.0], 諧振式電力電子轉換器[78.1], 無線通訊天線設計[77.2], 微帶天線專題[81.5], 微波感測專題[94.0], 視訊標準專題[95.0], 低功率積體電路專題[84.8], 高等類比積體電路設計[79.9], 醫學影像系統[81.7], 照明電子設計專題[86.1], 超大型積體電路數位訊號處理[89.3], 電腦視覺[86.7], 混合訊號積體電路設計專題[83.6], 生理訊號研究專題[87.0], 三維視覺[88.2]</t>
+          <t>生醫儀器導論[83.8], 高可靠度系統之設計、測試與應用[83.9], 書報討論[94.0,93.3], 光電元件[89.5], 固態電子元件（二）[79.7], 智慧型微感測晶片設計專題[88.0], 感測元件[89.3], 電子元件專題（二）[95.0], 薄膜工程專題[95.0], 先進元件可靠度專題[95.0], 奈米材料[95.0], 固態電子元件（三）[95.0], 二維半導體元件專題[95.0], 寬能隙半導體與功率元件[69.3], 希爾伯特空間方法與應用[70.7], 最佳控制[95.0], 模糊數學[95.0], 機器人學[75.8], 人工智慧（一）[87.0], 無線網路資源管理專題[95.0], 車載通訊網路技術與應用[95.0], 軟性計算[89.9], 3D內容生成與體感互動[95.0], 數據分析學專題[95.0], 數位化時代的開放式創新[70.2], 主動式電力濾波器[95.0], 電力系統專題[93.4], 電機機械系統設計專題[95.0], 配電系統分析專題[86.6], 電力系統規劃[82.0], 諧振式電力電子轉換器[78.1], 無線通訊天線設計[77.2], 微帶天線專題[81.5], 微波感測專題[94.0], 視訊標準專題[95.0], 低功率積體電路專題[84.8], 高等類比積體電路設計[79.9], 醫學影像系統[81.7], 照明電子設計專題[86.1], 超大型積體電路數位訊號處理[89.3], 電腦視覺[86.7], 混合訊號積體電路設計專題[83.6], 生理訊號研究專題[87.0], 三維視覺[88.2]</t>
         </is>
       </c>
       <c r="C6" s="8" t="n">
